--- a/artifacts/results/LLM Responses with Ragas.xlsx
+++ b/artifacts/results/LLM Responses with Ragas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/sm11926_uga_edu/Documents/GNEM_Project/evAutomationUpdated-2/artifacts/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{5CA93A4C-5515-9B47-86C1-52A6AFDCDE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B6DC351-6887-F145-B37A-C625FF9DD52B}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{5CA93A4C-5515-9B47-86C1-52A6AFDCDE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFF0B98-3888-484B-B780-E42AEBD7ED10}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{DAC7565A-F3CD-8145-81DA-9309A3E78983}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="814">
   <si>
     <t>List all companies located in Troup County and include their Category, EV Supply Chain Role, and Employment.</t>
   </si>
@@ -4925,12 +4925,6 @@
 * ...and so on.</t>
   </si>
   <si>
-    <t>I do not have access to a real-time, comprehensive database of all companies globally and their primary facility types. Therefore, I cannot generate this specific list.</t>
-  </si>
-  <si>
-    <t>Please specify which headquarters you are referring to. I need the name of the organization or company to provide its Location and Employment.</t>
-  </si>
-  <si>
     <t>Here are companies with a primary facility type focused on R&amp;D, along with their associated EV Supply Chain Roles:
 * **QuantumScape:** Battery Technology/Materials (solid-state batteries)
 * **Solid Power:** Battery Technology/Materials (solid-state batteries)
@@ -5777,6 +5771,9 @@
   </si>
   <si>
     <t>gemini_no_rag</t>
+  </si>
+  <si>
+    <t>I do not have access to a real-time, comprehensive database of all companies globally and their primary facility types. Therefore, I cannot generate this specific list. Please specify which headquarters you are referring to. I need the name of the organization or company to provide its Location and Employment.</t>
   </si>
 </sst>
 </file>
@@ -6203,11 +6200,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF203B46-616E-F741-BC4B-4E115A445F84}">
-  <dimension ref="A1:AE1000"/>
+  <dimension ref="A1:AE999"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="37.1640625" customWidth="1"/>
+    <col min="3" max="28" width="0" hidden="1" customWidth="1"/>
     <col min="29" max="29" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6297,10 +6295,10 @@
         <v>622</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>556</v>
       </c>
@@ -8176,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="AC22" s="5" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="136" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -8264,11 +8262,11 @@
       <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AC23" s="5" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="136" x14ac:dyDescent="0.2">
+      <c r="AC23" s="4" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>71</v>
       </c>
@@ -8354,10 +8352,10 @@
         <v>0</v>
       </c>
       <c r="AC24" s="4" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" ht="409.6" x14ac:dyDescent="0.2">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -8442,8 +8440,8 @@
       <c r="AB25">
         <v>0</v>
       </c>
-      <c r="AC25" s="4" t="s">
-        <v>736</v>
+      <c r="AC25" s="5" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
@@ -8532,10 +8530,10 @@
         <v>0</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="136" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -8620,11 +8618,11 @@
       <c r="AB27">
         <v>0</v>
       </c>
-      <c r="AC27" s="5" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="136" x14ac:dyDescent="0.2">
+      <c r="AC27" s="4" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>95</v>
       </c>
@@ -8709,11 +8707,11 @@
       <c r="AB28">
         <v>0</v>
       </c>
-      <c r="AC28" s="4" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AC28" s="5" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="136" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>101</v>
       </c>
@@ -8798,11 +8796,11 @@
       <c r="AB29">
         <v>0</v>
       </c>
-      <c r="AC29" s="5" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" ht="136" x14ac:dyDescent="0.2">
+      <c r="AC29" s="4" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="241" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -8888,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="AC30" s="4" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" ht="241" x14ac:dyDescent="0.2">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" ht="371" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>113</v>
       </c>
@@ -8977,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="AC31" s="4" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" ht="371" x14ac:dyDescent="0.2">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>119</v>
       </c>
@@ -9065,11 +9063,11 @@
       <c r="AB32">
         <v>0</v>
       </c>
-      <c r="AC32" s="4" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC32" s="5" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="196" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>125</v>
       </c>
@@ -9154,11 +9152,11 @@
       <c r="AB33">
         <v>0</v>
       </c>
-      <c r="AC33" s="5" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" ht="196" x14ac:dyDescent="0.2">
+      <c r="AC33" s="4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="151" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -9244,10 +9242,10 @@
         <v>0</v>
       </c>
       <c r="AC34" s="4" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="35" spans="1:29" ht="151" x14ac:dyDescent="0.2">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>137</v>
       </c>
@@ -9332,11 +9330,11 @@
       <c r="AB35">
         <v>0</v>
       </c>
-      <c r="AC35" s="4" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC35" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>143</v>
       </c>
@@ -9421,11 +9419,11 @@
       <c r="AB36">
         <v>0</v>
       </c>
-      <c r="AC36" s="5" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="37" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="AC36" s="4" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" ht="271" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>149</v>
       </c>
@@ -9511,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AC37" s="4" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="38" spans="1:29" ht="271" x14ac:dyDescent="0.2">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" ht="226" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -9600,10 +9598,10 @@
         <v>0</v>
       </c>
       <c r="AC38" s="4" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" ht="226" x14ac:dyDescent="0.2">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" ht="211" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>160</v>
       </c>
@@ -9689,10 +9687,10 @@
         <v>0</v>
       </c>
       <c r="AC39" s="4" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29" ht="211" x14ac:dyDescent="0.2">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" ht="357" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>166</v>
       </c>
@@ -9778,10 +9776,10 @@
         <v>0</v>
       </c>
       <c r="AC40" s="4" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="41" spans="1:29" ht="357" x14ac:dyDescent="0.2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" ht="121" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -9867,10 +9865,10 @@
         <v>0</v>
       </c>
       <c r="AC41" s="4" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29" ht="121" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" ht="46" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>178</v>
       </c>
@@ -9956,10 +9954,10 @@
         <v>0</v>
       </c>
       <c r="AC42" s="4" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="43" spans="1:29" ht="46" x14ac:dyDescent="0.2">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="136" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>184</v>
       </c>
@@ -10045,10 +10043,10 @@
         <v>0</v>
       </c>
       <c r="AC43" s="4" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" ht="136" x14ac:dyDescent="0.2">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="166" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>190</v>
       </c>
@@ -10134,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="AC44" s="4" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" ht="166" x14ac:dyDescent="0.2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" ht="91" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>196</v>
       </c>
@@ -10223,10 +10221,10 @@
         <v>0</v>
       </c>
       <c r="AC45" s="4" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="46" spans="1:29" ht="91" x14ac:dyDescent="0.2">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>201</v>
       </c>
@@ -10311,8 +10309,8 @@
       <c r="AB46">
         <v>0</v>
       </c>
-      <c r="AC46" s="4" t="s">
-        <v>757</v>
+      <c r="AC46" s="5" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
@@ -10401,10 +10399,10 @@
         <v>0</v>
       </c>
       <c r="AC47" s="5" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" ht="343" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>213</v>
       </c>
@@ -10489,11 +10487,11 @@
       <c r="AB48">
         <v>0</v>
       </c>
-      <c r="AC48" s="5" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="343" x14ac:dyDescent="0.2">
+      <c r="AC48" s="4" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29" ht="136" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>219</v>
       </c>
@@ -10579,10 +10577,10 @@
         <v>0</v>
       </c>
       <c r="AC49" s="4" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" ht="136" x14ac:dyDescent="0.2">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="329" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>225</v>
       </c>
@@ -10668,10 +10666,10 @@
         <v>0</v>
       </c>
       <c r="AC50" s="4" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="51" spans="1:29" ht="329" x14ac:dyDescent="0.2">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" ht="91" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>231</v>
       </c>
@@ -10757,10 +10755,10 @@
         <v>0</v>
       </c>
       <c r="AC51" s="4" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" ht="91" x14ac:dyDescent="0.2">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" ht="181" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>237</v>
       </c>
@@ -10846,10 +10844,10 @@
         <v>0</v>
       </c>
       <c r="AC52" s="4" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" ht="181" x14ac:dyDescent="0.2">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" ht="211" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>243</v>
       </c>
@@ -10935,10 +10933,10 @@
         <v>0</v>
       </c>
       <c r="AC53" s="4" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29" ht="211" x14ac:dyDescent="0.2">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" ht="46" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>249</v>
       </c>
@@ -11024,10 +11022,10 @@
         <v>0</v>
       </c>
       <c r="AC54" s="4" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" ht="46" x14ac:dyDescent="0.2">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>255</v>
       </c>
@@ -11112,11 +11110,11 @@
       <c r="AB55">
         <v>0</v>
       </c>
-      <c r="AC55" s="4" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC55" s="5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" ht="106" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>261</v>
       </c>
@@ -11201,8 +11199,8 @@
       <c r="AB56">
         <v>0</v>
       </c>
-      <c r="AC56" s="5" t="s">
-        <v>767</v>
+      <c r="AC56" s="4" t="s">
+        <v>766</v>
       </c>
     </row>
     <row r="57" spans="1:29" ht="106" x14ac:dyDescent="0.2">
@@ -11291,10 +11289,10 @@
         <v>0</v>
       </c>
       <c r="AC57" s="4" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" ht="106" x14ac:dyDescent="0.2">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" ht="91" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>273</v>
       </c>
@@ -11380,10 +11378,10 @@
         <v>0</v>
       </c>
       <c r="AC58" s="4" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" ht="91" x14ac:dyDescent="0.2">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>279</v>
       </c>
@@ -11468,8 +11466,8 @@
       <c r="AB59">
         <v>0</v>
       </c>
-      <c r="AC59" s="4" t="s">
-        <v>770</v>
+      <c r="AC59" s="5" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
@@ -11558,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="AC60" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
@@ -11647,7 +11645,7 @@
         <v>0</v>
       </c>
       <c r="AC61" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
@@ -11736,10 +11734,10 @@
         <v>0</v>
       </c>
       <c r="AC62" s="5" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="63" spans="1:29" ht="46" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>303</v>
       </c>
@@ -11824,11 +11822,11 @@
       <c r="AB63">
         <v>0</v>
       </c>
-      <c r="AC63" s="5" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29" ht="46" x14ac:dyDescent="0.2">
+      <c r="AC63" s="4" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="64" spans="1:29" ht="151" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>309</v>
       </c>
@@ -11914,10 +11912,10 @@
         <v>0</v>
       </c>
       <c r="AC64" s="4" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29" ht="151" x14ac:dyDescent="0.2">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="65" spans="1:29" ht="271" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>315</v>
       </c>
@@ -12003,10 +12001,10 @@
         <v>0</v>
       </c>
       <c r="AC65" s="4" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29" ht="271" x14ac:dyDescent="0.2">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>321</v>
       </c>
@@ -12091,8 +12089,8 @@
       <c r="AB66">
         <v>0</v>
       </c>
-      <c r="AC66" s="4" t="s">
-        <v>777</v>
+      <c r="AC66" s="5" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
@@ -12181,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="AC67" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
@@ -12270,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="AC68" s="5" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="69" spans="1:29" ht="76" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>339</v>
       </c>
@@ -12358,11 +12356,11 @@
       <c r="AB69">
         <v>0</v>
       </c>
-      <c r="AC69" s="5" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29" ht="76" x14ac:dyDescent="0.2">
+      <c r="AC69" s="4" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>345</v>
       </c>
@@ -12447,11 +12445,11 @@
       <c r="AB70">
         <v>0</v>
       </c>
-      <c r="AC70" s="4" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC70" s="5" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="71" spans="1:29" ht="76" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>351</v>
       </c>
@@ -12536,11 +12534,11 @@
       <c r="AB71">
         <v>0</v>
       </c>
-      <c r="AC71" s="5" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="76" x14ac:dyDescent="0.2">
+      <c r="AC71" s="4" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="72" spans="1:29" ht="226" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>357</v>
       </c>
@@ -12626,10 +12624,10 @@
         <v>0</v>
       </c>
       <c r="AC72" s="4" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29" ht="226" x14ac:dyDescent="0.2">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="73" spans="1:29" ht="121" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>363</v>
       </c>
@@ -12715,10 +12713,10 @@
         <v>0</v>
       </c>
       <c r="AC73" s="4" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" ht="121" x14ac:dyDescent="0.2">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" ht="31" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>369</v>
       </c>
@@ -12804,10 +12802,10 @@
         <v>0</v>
       </c>
       <c r="AC74" s="4" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="75" spans="1:29" ht="31" x14ac:dyDescent="0.2">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="75" spans="1:29" ht="106" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>375</v>
       </c>
@@ -12893,10 +12891,10 @@
         <v>0</v>
       </c>
       <c r="AC75" s="4" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29" ht="106" x14ac:dyDescent="0.2">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>381</v>
       </c>
@@ -12981,11 +12979,11 @@
       <c r="AB76">
         <v>0</v>
       </c>
-      <c r="AC76" s="4" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC76" s="5" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" ht="371" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>387</v>
       </c>
@@ -13070,11 +13068,11 @@
       <c r="AB77">
         <v>0</v>
       </c>
-      <c r="AC77" s="5" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" ht="371" x14ac:dyDescent="0.2">
+      <c r="AC77" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>393</v>
       </c>
@@ -13159,11 +13157,11 @@
       <c r="AB78">
         <v>0</v>
       </c>
-      <c r="AC78" s="4" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC78" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" ht="226" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>399</v>
       </c>
@@ -13248,11 +13246,11 @@
       <c r="AB79">
         <v>0</v>
       </c>
-      <c r="AC79" s="5" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" ht="226" x14ac:dyDescent="0.2">
+      <c r="AC79" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>405</v>
       </c>
@@ -13337,11 +13335,11 @@
       <c r="AB80">
         <v>0</v>
       </c>
-      <c r="AC80" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC80" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" ht="166" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>411</v>
       </c>
@@ -13426,11 +13424,11 @@
       <c r="AB81">
         <v>0</v>
       </c>
-      <c r="AC81" s="5" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="166" x14ac:dyDescent="0.2">
+      <c r="AC81" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>417</v>
       </c>
@@ -13516,10 +13514,10 @@
         <v>0</v>
       </c>
       <c r="AC82" s="4" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="83" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" ht="91" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>423</v>
       </c>
@@ -13605,10 +13603,10 @@
         <v>0</v>
       </c>
       <c r="AC83" s="4" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="84" spans="1:29" ht="91" x14ac:dyDescent="0.2">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" ht="151" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>429</v>
       </c>
@@ -13694,10 +13692,10 @@
         <v>0</v>
       </c>
       <c r="AC84" s="4" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="151" x14ac:dyDescent="0.2">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" ht="357" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>435</v>
       </c>
@@ -13783,10 +13781,10 @@
         <v>0</v>
       </c>
       <c r="AC85" s="4" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="357" x14ac:dyDescent="0.2">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" ht="343" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>441</v>
       </c>
@@ -13872,10 +13870,10 @@
         <v>0</v>
       </c>
       <c r="AC86" s="4" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="343" x14ac:dyDescent="0.2">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" ht="136" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>447</v>
       </c>
@@ -13961,10 +13959,10 @@
         <v>0</v>
       </c>
       <c r="AC87" s="4" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="136" x14ac:dyDescent="0.2">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" ht="196" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>452</v>
       </c>
@@ -14050,10 +14048,10 @@
         <v>0</v>
       </c>
       <c r="AC88" s="4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="196" x14ac:dyDescent="0.2">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" ht="343" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>458</v>
       </c>
@@ -14139,10 +14137,10 @@
         <v>0</v>
       </c>
       <c r="AC89" s="4" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" ht="343" x14ac:dyDescent="0.2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" ht="271" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>464</v>
       </c>
@@ -14228,10 +14226,10 @@
         <v>0</v>
       </c>
       <c r="AC90" s="4" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="271" x14ac:dyDescent="0.2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>470</v>
       </c>
@@ -14317,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="AC91" s="4" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>476</v>
       </c>
@@ -14405,8 +14403,8 @@
       <c r="AB92">
         <v>0</v>
       </c>
-      <c r="AC92" s="4" t="s">
-        <v>803</v>
+      <c r="AC92" s="5" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="93" spans="1:29" x14ac:dyDescent="0.2">
@@ -14495,7 +14493,7 @@
         <v>0</v>
       </c>
       <c r="AC93" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="94" spans="1:29" x14ac:dyDescent="0.2">
@@ -14584,10 +14582,10 @@
         <v>0</v>
       </c>
       <c r="AC94" s="5" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" ht="46" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>493</v>
       </c>
@@ -14672,11 +14670,11 @@
       <c r="AB95">
         <v>0</v>
       </c>
-      <c r="AC95" s="5" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" ht="46" x14ac:dyDescent="0.2">
+      <c r="AC95" s="4" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>499</v>
       </c>
@@ -14761,11 +14759,11 @@
       <c r="AB96">
         <v>0</v>
       </c>
-      <c r="AC96" s="4" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC96" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="97" spans="1:29" ht="271" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>505</v>
       </c>
@@ -14850,11 +14848,11 @@
       <c r="AB97">
         <v>0</v>
       </c>
-      <c r="AC97" s="5" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" ht="271" x14ac:dyDescent="0.2">
+      <c r="AC97" s="4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="98" spans="1:29" ht="46" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>511</v>
       </c>
@@ -14940,10 +14938,10 @@
         <v>0</v>
       </c>
       <c r="AC98" s="4" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" ht="46" x14ac:dyDescent="0.2">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="99" spans="1:29" ht="226" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>517</v>
       </c>
@@ -15029,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="AC99" s="4" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" ht="226" x14ac:dyDescent="0.2">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="100" spans="1:29" ht="121" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>523</v>
       </c>
@@ -15118,10 +15116,10 @@
         <v>0</v>
       </c>
       <c r="AC100" s="4" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" ht="121" x14ac:dyDescent="0.2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>529</v>
       </c>
@@ -15206,14 +15204,12 @@
       <c r="AB101">
         <v>0</v>
       </c>
-      <c r="AC101" s="4" t="s">
-        <v>812</v>
+      <c r="AC101" s="5" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="102" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="AC102" s="5" t="s">
-        <v>813</v>
-      </c>
+      <c r="AC102" s="6"/>
     </row>
     <row r="103" spans="1:29" x14ac:dyDescent="0.2">
       <c r="AC103" s="6"/>
@@ -17905,9 +17901,6 @@
     </row>
     <row r="999" spans="29:29" x14ac:dyDescent="0.2">
       <c r="AC999" s="6"/>
-    </row>
-    <row r="1000" spans="29:29" x14ac:dyDescent="0.2">
-      <c r="AC1000" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/results/LLM Responses with Ragas.xlsx
+++ b/artifacts/results/LLM Responses with Ragas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://outlookuga-my.sharepoint.com/personal/sm11926_uga_edu/Documents/GNEM_Project/evAutomationUpdated-2/artifacts/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{5CA93A4C-5515-9B47-86C1-52A6AFDCDE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFF0B98-3888-484B-B780-E42AEBD7ED10}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{5CA93A4C-5515-9B47-86C1-52A6AFDCDE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FBED3A6-6AD9-3442-9826-FE4249A74E09}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{DAC7565A-F3CD-8145-81DA-9309A3E78983}"/>
   </bookViews>
@@ -5877,10 +5877,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6205,7 +6201,27 @@
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="37.1640625" customWidth="1"/>
-    <col min="3" max="28" width="0" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="53.83203125" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" customWidth="1"/>
+    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="50.5" customWidth="1"/>
+    <col min="8" max="8" width="25.5" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+    <col min="10" max="10" width="28.33203125" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" customWidth="1"/>
+    <col min="12" max="12" width="35.33203125" customWidth="1"/>
+    <col min="13" max="13" width="24.6640625" customWidth="1"/>
+    <col min="14" max="14" width="19.5" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="20.5" customWidth="1"/>
+    <col min="17" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="29.83203125" customWidth="1"/>
+    <col min="20" max="20" width="6.83203125" customWidth="1"/>
+    <col min="21" max="21" width="13.33203125" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="28" width="10.83203125" customWidth="1"/>
     <col min="29" max="29" width="255.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6743,7 +6759,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>586</v>
       </c>
@@ -7188,7 +7204,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
